--- a/storage/app/import/new-kevis/kevis.xlsx
+++ b/storage/app/import/new-kevis/kevis.xlsx
@@ -759,10 +759,10 @@
     </row>
     <row r="2" spans="1:22">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
         <v>2</v>
@@ -807,24 +807,24 @@
         <v>12</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="T2" s="1" t="s">
         <v>98</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:22">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
         <v>2</v>
@@ -869,16 +869,16 @@
         <v>12</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="T3" s="1" t="s">
         <v>98</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:22">

--- a/storage/app/import/new-kevis/kevis.xlsx
+++ b/storage/app/import/new-kevis/kevis.xlsx
@@ -774,7 +774,7 @@
         <v>6</v>
       </c>
       <c r="F2">
-        <v>1790</v>
+        <v>1540</v>
       </c>
       <c r="I2" t="s">
         <v>16</v>
@@ -836,7 +836,7 @@
         <v>6</v>
       </c>
       <c r="F3">
-        <v>1790</v>
+        <v>1540</v>
       </c>
       <c r="I3" t="s">
         <v>16</v>
@@ -898,7 +898,7 @@
         <v>6</v>
       </c>
       <c r="F4">
-        <v>1790</v>
+        <v>1540</v>
       </c>
       <c r="I4" t="s">
         <v>16</v>
@@ -960,7 +960,7 @@
         <v>6</v>
       </c>
       <c r="F5">
-        <v>1790</v>
+        <v>1540</v>
       </c>
       <c r="I5" t="s">
         <v>16</v>
@@ -1022,7 +1022,7 @@
         <v>6</v>
       </c>
       <c r="F6">
-        <v>1790</v>
+        <v>1540</v>
       </c>
       <c r="I6" t="s">
         <v>16</v>
@@ -1084,7 +1084,7 @@
         <v>6</v>
       </c>
       <c r="F7">
-        <v>1690</v>
+        <v>1440</v>
       </c>
       <c r="I7" t="s">
         <v>16</v>
@@ -1146,7 +1146,7 @@
         <v>6</v>
       </c>
       <c r="F8">
-        <v>1790</v>
+        <v>1540</v>
       </c>
       <c r="I8" t="s">
         <v>16</v>
@@ -1208,7 +1208,7 @@
         <v>6</v>
       </c>
       <c r="F9">
-        <v>1790</v>
+        <v>1540</v>
       </c>
       <c r="I9" t="s">
         <v>16</v>
@@ -1270,7 +1270,7 @@
         <v>6</v>
       </c>
       <c r="F10">
-        <v>1790</v>
+        <v>1540</v>
       </c>
       <c r="I10" t="s">
         <v>16</v>
@@ -1332,7 +1332,7 @@
         <v>6</v>
       </c>
       <c r="F11">
-        <v>1690</v>
+        <v>1440</v>
       </c>
       <c r="I11" t="s">
         <v>16</v>
@@ -1394,7 +1394,7 @@
         <v>6</v>
       </c>
       <c r="F12">
-        <v>1690</v>
+        <v>1440</v>
       </c>
       <c r="I12" t="s">
         <v>16</v>
@@ -1456,7 +1456,7 @@
         <v>6</v>
       </c>
       <c r="F13">
-        <v>1790</v>
+        <v>1540</v>
       </c>
       <c r="I13" t="s">
         <v>16</v>
@@ -1518,7 +1518,7 @@
         <v>6</v>
       </c>
       <c r="F14">
-        <v>1790</v>
+        <v>1540</v>
       </c>
       <c r="I14" t="s">
         <v>16</v>
@@ -1580,7 +1580,7 @@
         <v>6</v>
       </c>
       <c r="F15">
-        <v>1790</v>
+        <v>1540</v>
       </c>
       <c r="I15" t="s">
         <v>16</v>
@@ -1642,7 +1642,7 @@
         <v>6</v>
       </c>
       <c r="F16">
-        <v>1690</v>
+        <v>1440</v>
       </c>
       <c r="I16" t="s">
         <v>16</v>
